--- a/data/trans_orig/P16B13-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16B13-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2007</t>
+          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2007 (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39863</t>
+          <t>41102</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64808</t>
+          <t>64437</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71597</t>
+          <t>71605</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>108995</t>
+          <t>108966</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117478</t>
+          <t>117421</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6082</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>884</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17720</t>
+          <t>18064</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32626</t>
+          <t>32655</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39266</t>
+          <t>39276</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54212</t>
+          <t>54983</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62931</t>
+          <t>62912</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>863</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>7484</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>996</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9696</t>
+          <t>8925</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8763</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6841</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15764</t>
+          <t>15938</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,62 +1566,62 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1526</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1590</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>6667</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>6,75%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1526</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>6841</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,49%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75049</t>
+          <t>75807</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84577</t>
+          <t>84582</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>107798</t>
+          <t>108176</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117533</t>
+          <t>117503</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>188423</t>
+          <t>187776</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>200356</t>
+          <t>200197</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>895</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16524</t>
+          <t>17171</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2012</t>
+          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62224</t>
+          <t>62689</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>107634</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>109616</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>171100</t>
+          <t>171978</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,62 +2483,62 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>4584</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>5462</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40477</t>
+          <t>41859</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52008</t>
+          <t>52626</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49210</t>
+          <t>50228</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94001</t>
+          <t>94341</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107095</t>
+          <t>107308</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15074</t>
+          <t>13692</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17864</t>
+          <t>17524</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8570</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19042</t>
+          <t>19237</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30520</t>
+          <t>31452</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41061</t>
+          <t>40957</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>8540</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>975</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11412</t>
+          <t>10480</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>120311</t>
+          <t>120219</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>135496</t>
+          <t>134559</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>182076</t>
+          <t>182299</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>189201</t>
+          <t>189197</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>305713</t>
+          <t>306978</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>322735</t>
+          <t>322831</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>898</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8019</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24646</t>
+          <t>23381</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2016</t>
+          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2016 (tasa de respuesta: 97,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29915</t>
+          <t>30401</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63195</t>
+          <t>62156</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96661</t>
+          <t>96942</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6932</t>
+          <t>6651</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38686</t>
+          <t>38102</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46054</t>
+          <t>43951</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85822</t>
+          <t>86678</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>98894</t>
+          <t>98912</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>10731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14905</t>
+          <t>14049</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8447</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>12577</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24838</t>
+          <t>24903</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>6557</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83149</t>
+          <t>82439</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95153</t>
+          <t>95123</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>129107</t>
+          <t>129934</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>137993</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>216466</t>
+          <t>216815</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>231809</t>
+          <t>231392</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13705</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>964</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19345</t>
+          <t>18996</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16B13-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16B13-Estudios-trans_orig.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41102</t>
+          <t>40500</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64437</t>
+          <t>64338</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71605</t>
+          <t>71596</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>108966</t>
+          <t>108986</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117421</t>
+          <t>117496</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>893</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>8151</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>938</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9468</t>
+          <t>9448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18064</t>
+          <t>18280</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32655</t>
+          <t>32392</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39276</t>
+          <t>39268</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54983</t>
+          <t>55078</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62912</t>
+          <t>62940</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>5489</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>871</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7484</t>
+          <t>7747</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>968</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8925</t>
+          <t>8830</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>8275</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15938</t>
+          <t>15397</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>7208</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>31,89%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75807</t>
+          <t>75932</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84582</t>
+          <t>84579</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>108176</t>
+          <t>107718</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117503</t>
+          <t>117488</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>187776</t>
+          <t>188176</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>200197</t>
+          <t>200566</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>898</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>9545</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11293</t>
+          <t>11751</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17171</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62689</t>
+          <t>61568</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>171978</t>
+          <t>171549</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>5378</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41859</t>
+          <t>41108</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52626</t>
+          <t>52254</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50228</t>
+          <t>49460</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94341</t>
+          <t>94305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107308</t>
+          <t>107192</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13692</t>
+          <t>14443</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6854</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17524</t>
+          <t>17560</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>9418</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19237</t>
+          <t>19353</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31452</t>
+          <t>31667</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40957</t>
+          <t>40990</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>942</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10480</t>
+          <t>10265</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>120219</t>
+          <t>119434</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>134559</t>
+          <t>134738</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>182299</t>
+          <t>182112</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>189197</t>
+          <t>189200</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>306978</t>
+          <t>306537</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>322831</t>
+          <t>322736</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20044</t>
+          <t>20829</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>895</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>7983</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7528</t>
+          <t>7623</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23381</t>
+          <t>23822</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30401</t>
+          <t>30094</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62156</t>
+          <t>62921</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96942</t>
+          <t>95891</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>6430</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>7702</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38102</t>
+          <t>38399</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43951</t>
+          <t>45957</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86678</t>
+          <t>86314</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>98912</t>
+          <t>98884</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10731</t>
+          <t>10434</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>5937</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14049</t>
+          <t>14413</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7222</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12577</t>
+          <t>13906</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24903</t>
+          <t>24937</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82439</t>
+          <t>82662</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95123</t>
+          <t>95132</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>129934</t>
+          <t>129597</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>137993</t>
+          <t>138012</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>216815</t>
+          <t>217492</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>231392</t>
+          <t>231574</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14415</t>
+          <t>14192</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18996</t>
+          <t>18319</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
